--- a/Working/Tesis 1.xlsx
+++ b/Working/Tesis 1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sbobi/Desktop/Tesis-Master/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sbobi/Desktop/Tesis-Master/Working/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00828AF6-A54D-AB46-9708-F9E41567FEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB4C89C-76CB-BC4A-8DC5-C92F0546B45A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{6F376A92-3992-B74D-B5D7-33E7F64B4F36}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="543">
   <si>
     <t>Areas</t>
   </si>
@@ -2059,6 +2059,15 @@
   </si>
   <si>
     <t>Las cadenas de herramientas de seguridad automatizadas son indispensables; el futuro reside en la integración de IA y Machine Learning para la detección autónoma de amenazas y remediación automática.</t>
+  </si>
+  <si>
+    <t>Nos vamos a quedar solo con dependencias que sean de librerias activas, nada deprecado. Usando el versionamiento estandar</t>
+  </si>
+  <si>
+    <t>Además, vamos a pensar en mirar los cambios no entre versiones grandes, sino pequeñas.</t>
+  </si>
+  <si>
+    <t>Revisar el modelo del paper: Can we rtustt….</t>
   </si>
 </sst>
 </file>
@@ -2312,24 +2321,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2356,6 +2347,24 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2714,24 +2723,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="G2" s="27" t="s">
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="G2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="L2" s="27" t="s">
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="L2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
+      <c r="M2" s="36"/>
+      <c r="N2" s="36"/>
+      <c r="O2" s="36"/>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B3" s="2"/>
@@ -2857,22 +2866,22 @@
       <c r="O11" s="9"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
+      <c r="C13" s="37"/>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
+      <c r="O13" s="37"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="2"/>
@@ -2892,68 +2901,68 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" s="24"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
       <c r="O15" s="6"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="5"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
       <c r="O16" s="6"/>
     </row>
     <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
       <c r="O17" s="6"/>
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="6"/>
     </row>
     <row r="19" spans="2:15" x14ac:dyDescent="0.2">
@@ -2962,84 +2971,84 @@
     </row>
     <row r="20" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="33"/>
+      <c r="M20" s="33"/>
+      <c r="N20" s="33"/>
       <c r="O20" s="6"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="5"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
+      <c r="M21" s="33"/>
+      <c r="N21" s="33"/>
       <c r="O21" s="6"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="5"/>
-      <c r="C22" s="24"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="24"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="24"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
-      <c r="K22" s="24"/>
-      <c r="L22" s="24"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="24"/>
+      <c r="C22" s="33"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="33"/>
+      <c r="M22" s="33"/>
+      <c r="N22" s="33"/>
       <c r="O22" s="6"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="5"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="24"/>
-      <c r="F23" s="24"/>
-      <c r="G23" s="24"/>
-      <c r="H23" s="24"/>
-      <c r="I23" s="24"/>
-      <c r="J23" s="24"/>
-      <c r="K23" s="24"/>
-      <c r="L23" s="24"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="24"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="33"/>
+      <c r="M23" s="33"/>
+      <c r="N23" s="33"/>
       <c r="O23" s="6"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
-      <c r="C24" s="24"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="24"/>
-      <c r="F24" s="24"/>
-      <c r="G24" s="24"/>
-      <c r="H24" s="24"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
-      <c r="K24" s="24"/>
-      <c r="L24" s="24"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="24"/>
+      <c r="C24" s="33"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="33"/>
+      <c r="M24" s="33"/>
+      <c r="N24" s="33"/>
       <c r="O24" s="6"/>
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
@@ -3048,52 +3057,52 @@
     </row>
     <row r="26" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B26" s="5"/>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
-      <c r="F26" s="24"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="33"/>
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
       <c r="O26" s="6"/>
     </row>
     <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27" s="5"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="24"/>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
       <c r="O27" s="6"/>
     </row>
     <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" s="24"/>
-      <c r="K28" s="24"/>
-      <c r="L28" s="24"/>
-      <c r="M28" s="24"/>
-      <c r="N28" s="24"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
+      <c r="N28" s="33"/>
       <c r="O28" s="6"/>
     </row>
     <row r="29" spans="2:15" x14ac:dyDescent="0.2">
@@ -3127,71 +3136,71 @@
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
+      <c r="C31" s="38"/>
+      <c r="D31" s="38"/>
+      <c r="E31" s="38"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="38"/>
+      <c r="H31" s="38"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="38"/>
+      <c r="K31" s="38"/>
+      <c r="L31" s="38"/>
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="38"/>
     </row>
     <row r="32" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B32" s="5"/>
-      <c r="C32" s="25" t="s">
+      <c r="C32" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
       <c r="O32" s="6"/>
     </row>
     <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B33" s="5"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="25"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
       <c r="O33" s="6"/>
     </row>
     <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B34" s="7"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
-      <c r="F34" s="26"/>
-      <c r="G34" s="26"/>
-      <c r="H34" s="26"/>
-      <c r="I34" s="26"/>
-      <c r="J34" s="26"/>
-      <c r="K34" s="26"/>
-      <c r="L34" s="26"/>
-      <c r="M34" s="26"/>
-      <c r="N34" s="26"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
       <c r="O34" s="9"/>
     </row>
   </sheetData>
@@ -3228,26 +3237,26 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
-      <c r="K2" s="28"/>
-      <c r="L2" s="28"/>
-      <c r="M2" s="28"/>
-      <c r="N2" s="28"/>
-      <c r="O2" s="28"/>
-      <c r="P2" s="28"/>
-      <c r="Q2" s="28"/>
-      <c r="R2" s="28"/>
-      <c r="S2" s="28"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="37"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
       <c r="U2" s="17" t="s">
         <v>22</v>
       </c>
@@ -3257,24 +3266,24 @@
     </row>
     <row r="3" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B3" s="5"/>
-      <c r="C3" s="25" t="s">
+      <c r="C3" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="25"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
       <c r="S3" s="6"/>
       <c r="U3" s="17" t="s">
         <v>25</v>
@@ -3285,22 +3294,22 @@
     </row>
     <row r="4" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B4" s="5"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="25"/>
-      <c r="H4" s="25"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="25"/>
-      <c r="Q4" s="25"/>
-      <c r="R4" s="25"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="I4" s="34"/>
+      <c r="J4" s="34"/>
+      <c r="K4" s="34"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
       <c r="S4" s="6"/>
       <c r="U4" s="17" t="s">
         <v>27</v>
@@ -3311,22 +3320,22 @@
     </row>
     <row r="5" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
       <c r="S5" s="6"/>
       <c r="U5" s="17" t="s">
         <v>29</v>
@@ -3337,22 +3346,22 @@
     </row>
     <row r="6" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="25"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="25"/>
-      <c r="Q6" s="25"/>
-      <c r="R6" s="25"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="34"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
       <c r="S6" s="6"/>
       <c r="U6" s="17" t="s">
         <v>31</v>
@@ -3363,22 +3372,22 @@
     </row>
     <row r="7" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="25"/>
-      <c r="Q7" s="25"/>
-      <c r="R7" s="25"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
       <c r="S7" s="6"/>
       <c r="U7" s="17" t="s">
         <v>33</v>
@@ -3389,24 +3398,24 @@
     </row>
     <row r="8" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B8" s="5"/>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
       <c r="S8" s="6"/>
       <c r="U8" s="17" t="s">
         <v>36</v>
@@ -3417,22 +3426,22 @@
     </row>
     <row r="9" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B9" s="5"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="25"/>
-      <c r="Q9" s="25"/>
-      <c r="R9" s="25"/>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
+      <c r="I9" s="34"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="34"/>
+      <c r="P9" s="34"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
       <c r="S9" s="6"/>
       <c r="U9" s="17" t="s">
         <v>38</v>
@@ -3443,22 +3452,22 @@
     </row>
     <row r="10" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B10" s="5"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="25"/>
-      <c r="Q10" s="25"/>
-      <c r="R10" s="25"/>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="34"/>
+      <c r="K10" s="34"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="34"/>
+      <c r="N10" s="34"/>
+      <c r="O10" s="34"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
       <c r="S10" s="6"/>
       <c r="U10" s="17" t="s">
         <v>40</v>
@@ -3469,22 +3478,22 @@
     </row>
     <row r="11" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="25"/>
-      <c r="Q11" s="25"/>
-      <c r="R11" s="25"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="34"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="34"/>
+      <c r="K11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="34"/>
+      <c r="N11" s="34"/>
+      <c r="O11" s="34"/>
+      <c r="P11" s="34"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
       <c r="S11" s="6"/>
       <c r="U11" s="17" t="s">
         <v>42</v>
@@ -3495,87 +3504,87 @@
     </row>
     <row r="12" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B12" s="5"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="25"/>
-      <c r="Q12" s="25"/>
-      <c r="R12" s="25"/>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="34"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="34"/>
+      <c r="K12" s="34"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="34"/>
+      <c r="N12" s="34"/>
+      <c r="O12" s="34"/>
+      <c r="P12" s="34"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
       <c r="S12" s="6"/>
       <c r="U12" s="1"/>
     </row>
     <row r="13" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B13" s="5"/>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="25"/>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="25"/>
-      <c r="Q13" s="25"/>
-      <c r="R13" s="25"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
       <c r="S13" s="6"/>
       <c r="U13" s="1"/>
     </row>
     <row r="14" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B14" s="5"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="25"/>
-      <c r="H14" s="25"/>
-      <c r="I14" s="25"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="25"/>
-      <c r="Q14" s="25"/>
-      <c r="R14" s="25"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="34"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="34"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
       <c r="S14" s="6"/>
       <c r="U14" s="1"/>
     </row>
     <row r="15" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+      <c r="G15" s="34"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="34"/>
+      <c r="K15" s="34"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="34"/>
+      <c r="P15" s="34"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
       <c r="S15" s="6"/>
       <c r="U15" s="18" t="s">
         <v>175</v>
@@ -3583,22 +3592,22 @@
     </row>
     <row r="16" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B16" s="5"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="25"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="25"/>
-      <c r="N16" s="25"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="25"/>
-      <c r="Q16" s="25"/>
-      <c r="R16" s="25"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="34"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="34"/>
+      <c r="K16" s="34"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="34"/>
+      <c r="P16" s="34"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
       <c r="S16" s="6"/>
       <c r="U16" s="19" t="s">
         <v>45</v>
@@ -3609,22 +3618,22 @@
     </row>
     <row r="17" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="25"/>
-      <c r="H17" s="25"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="25"/>
-      <c r="K17" s="25"/>
-      <c r="L17" s="25"/>
-      <c r="M17" s="25"/>
-      <c r="N17" s="25"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="25"/>
-      <c r="Q17" s="25"/>
-      <c r="R17" s="25"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="34"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
       <c r="S17" s="6"/>
       <c r="U17" s="19" t="s">
         <v>47</v>
@@ -3635,24 +3644,24 @@
     </row>
     <row r="18" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="J18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="34"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
       <c r="S18" s="6"/>
       <c r="U18" s="19" t="s">
         <v>49</v>
@@ -3663,22 +3672,22 @@
     </row>
     <row r="19" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B19" s="5"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="25"/>
-      <c r="N19" s="25"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="25"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="25"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
       <c r="S19" s="6"/>
       <c r="U19" s="19" t="s">
         <v>51</v>
@@ -3689,22 +3698,22 @@
     </row>
     <row r="20" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B20" s="5"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="34"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
       <c r="S20" s="6"/>
       <c r="U20" s="19" t="s">
         <v>54</v>
@@ -3715,22 +3724,22 @@
     </row>
     <row r="21" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B21" s="5"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="25"/>
-      <c r="Q21" s="25"/>
-      <c r="R21" s="25"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
+      <c r="K21" s="34"/>
+      <c r="L21" s="34"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="34"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
       <c r="S21" s="6"/>
       <c r="U21" s="19" t="s">
         <v>56</v>
@@ -3741,22 +3750,22 @@
     </row>
     <row r="22" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B22" s="5"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="25"/>
-      <c r="H22" s="25"/>
-      <c r="I22" s="25"/>
-      <c r="J22" s="25"/>
-      <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="25"/>
-      <c r="N22" s="25"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="25"/>
-      <c r="Q22" s="25"/>
-      <c r="R22" s="25"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
       <c r="S22" s="6"/>
       <c r="U22" s="19" t="s">
         <v>58</v>
@@ -3767,24 +3776,24 @@
     </row>
     <row r="23" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B23" s="5"/>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="25"/>
-      <c r="H23" s="25"/>
-      <c r="I23" s="25"/>
-      <c r="J23" s="25"/>
-      <c r="K23" s="25"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="25"/>
-      <c r="N23" s="25"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="25"/>
-      <c r="R23" s="25"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
       <c r="S23" s="6"/>
       <c r="U23" s="19" t="s">
         <v>60</v>
@@ -3795,22 +3804,22 @@
     </row>
     <row r="24" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="25"/>
-      <c r="H24" s="25"/>
-      <c r="I24" s="25"/>
-      <c r="J24" s="25"/>
-      <c r="K24" s="25"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="25"/>
-      <c r="N24" s="25"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="25"/>
-      <c r="Q24" s="25"/>
-      <c r="R24" s="25"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+      <c r="G24" s="34"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="34"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="34"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="34"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="34"/>
       <c r="S24" s="6"/>
       <c r="U24" s="19" t="s">
         <v>62</v>
@@ -3821,22 +3830,22 @@
     </row>
     <row r="25" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="J25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-      <c r="R25" s="25"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+      <c r="G25" s="34"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="34"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="34"/>
+      <c r="O25" s="34"/>
+      <c r="P25" s="34"/>
+      <c r="Q25" s="34"/>
+      <c r="R25" s="34"/>
       <c r="S25" s="6"/>
       <c r="U25" s="19" t="s">
         <v>65</v>
@@ -3847,22 +3856,22 @@
     </row>
     <row r="26" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B26" s="5"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="25"/>
-      <c r="Q26" s="25"/>
-      <c r="R26" s="25"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="34"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="34"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="34"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="34"/>
       <c r="S26" s="6"/>
       <c r="U26" s="19" t="s">
         <v>67</v>
@@ -3873,22 +3882,22 @@
     </row>
     <row r="27" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B27" s="5"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
       <c r="S27" s="6"/>
       <c r="U27" s="19" t="s">
         <v>69</v>
@@ -3899,24 +3908,24 @@
     </row>
     <row r="28" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
-      <c r="C28" s="25" t="s">
+      <c r="C28" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="25"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="25"/>
-      <c r="N28" s="25"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="25"/>
-      <c r="Q28" s="25"/>
-      <c r="R28" s="25"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="34"/>
+      <c r="M28" s="34"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="34"/>
+      <c r="P28" s="34"/>
+      <c r="Q28" s="34"/>
+      <c r="R28" s="34"/>
       <c r="S28" s="6"/>
       <c r="U28" s="19" t="s">
         <v>71</v>
@@ -3927,43 +3936,43 @@
     </row>
     <row r="29" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B29" s="5"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="25"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="25"/>
-      <c r="Q29" s="25"/>
-      <c r="R29" s="25"/>
+      <c r="C29" s="34"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
+      <c r="O29" s="34"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="34"/>
+      <c r="R29" s="34"/>
       <c r="S29" s="6"/>
       <c r="U29" s="1"/>
     </row>
     <row r="30" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="25"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="25"/>
-      <c r="Q30" s="25"/>
-      <c r="R30" s="25"/>
+      <c r="C30" s="34"/>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
       <c r="S30" s="6"/>
       <c r="U30" s="18" t="s">
         <v>74</v>
@@ -3971,22 +3980,22 @@
     </row>
     <row r="31" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B31" s="5"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="25"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="25"/>
-      <c r="Q31" s="25"/>
-      <c r="R31" s="25"/>
+      <c r="C31" s="34"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
+      <c r="O31" s="34"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="34"/>
+      <c r="R31" s="34"/>
       <c r="S31" s="6"/>
       <c r="U31" s="19" t="s">
         <v>45</v>
@@ -3997,22 +4006,22 @@
     </row>
     <row r="32" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B32" s="5"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="25"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="25"/>
-      <c r="Q32" s="25"/>
-      <c r="R32" s="25"/>
+      <c r="C32" s="34"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
       <c r="S32" s="6"/>
       <c r="U32" s="19" t="s">
         <v>47</v>
@@ -4033,24 +4042,24 @@
     </row>
     <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B34" s="5"/>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="25"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="25"/>
-      <c r="Q34" s="25"/>
-      <c r="R34" s="25"/>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
       <c r="S34" s="6"/>
       <c r="U34" s="19" t="s">
         <v>51</v>
@@ -4061,22 +4070,22 @@
     </row>
     <row r="35" spans="2:22" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B35" s="5"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="25"/>
-      <c r="L35" s="25"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="25"/>
-      <c r="Q35" s="25"/>
-      <c r="R35" s="25"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
       <c r="S35" s="6"/>
       <c r="U35" s="19" t="s">
         <v>54</v>
@@ -4910,17 +4919,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" ht="15.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
       <c r="L2" s="17" t="s">
         <v>175</v>
       </c>
@@ -4929,15 +4938,15 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29"/>
       <c r="L3" s="17" t="s">
         <v>74</v>
       </c>
@@ -4946,15 +4955,15 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="29"/>
       <c r="L4" s="17" t="s">
         <v>176</v>
       </c>
@@ -4963,15 +4972,15 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
       <c r="L5" s="17" t="s">
         <v>177</v>
       </c>
@@ -4980,15 +4989,15 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="17" t="s">
         <v>89</v>
       </c>
@@ -4997,15 +5006,15 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
       <c r="L7" s="17" t="s">
         <v>103</v>
       </c>
@@ -5030,6 +5039,9 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>542</v>
+      </c>
       <c r="L10" s="17" t="s">
         <v>144</v>
       </c>
@@ -6243,17 +6255,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>172</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
       <c r="L2" s="17" t="s">
         <v>175</v>
       </c>
@@ -6262,15 +6274,15 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29"/>
       <c r="L3" s="17" t="s">
         <v>74</v>
       </c>
@@ -6279,15 +6291,15 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="29"/>
       <c r="L4" s="17" t="s">
         <v>176</v>
       </c>
@@ -6296,15 +6308,15 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
       <c r="L5" s="17" t="s">
         <v>177</v>
       </c>
@@ -6313,15 +6325,15 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="17" t="s">
         <v>89</v>
       </c>
@@ -6330,15 +6342,15 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
       <c r="L7" s="17" t="s">
         <v>103</v>
       </c>
@@ -6352,6 +6364,9 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B10" s="1" t="s">
+        <v>540</v>
+      </c>
       <c r="L10" s="19" t="s">
         <v>45</v>
       </c>
@@ -6360,6 +6375,9 @@
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="B11" s="1" t="s">
+        <v>541</v>
+      </c>
       <c r="L11" s="19" t="s">
         <v>47</v>
       </c>
@@ -7038,17 +7056,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>173</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
       <c r="L2" s="17" t="s">
         <v>175</v>
       </c>
@@ -7057,15 +7075,15 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29"/>
       <c r="L3" s="17" t="s">
         <v>74</v>
       </c>
@@ -7074,15 +7092,15 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="29"/>
       <c r="L4" s="17" t="s">
         <v>176</v>
       </c>
@@ -7091,15 +7109,15 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
       <c r="L5" s="17" t="s">
         <v>177</v>
       </c>
@@ -7108,15 +7126,15 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="17" t="s">
         <v>89</v>
       </c>
@@ -7125,15 +7143,15 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
       <c r="L7" s="17" t="s">
         <v>103</v>
       </c>
@@ -7841,17 +7859,17 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="26"/>
       <c r="L2" s="17" t="s">
         <v>175</v>
       </c>
@@ -7860,15 +7878,15 @@
       </c>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B3" s="33"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="35"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="29"/>
       <c r="L3" s="17" t="s">
         <v>74</v>
       </c>
@@ -7877,15 +7895,15 @@
       </c>
     </row>
     <row r="4" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B4" s="33"/>
-      <c r="C4" s="34"/>
-      <c r="D4" s="34"/>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="35"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="29"/>
       <c r="L4" s="17" t="s">
         <v>176</v>
       </c>
@@ -7894,15 +7912,15 @@
       </c>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B5" s="33"/>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="35"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="29"/>
       <c r="L5" s="17" t="s">
         <v>177</v>
       </c>
@@ -7911,15 +7929,15 @@
       </c>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B6" s="33"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
-      <c r="J6" s="35"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="29"/>
       <c r="L6" s="17" t="s">
         <v>89</v>
       </c>
@@ -7928,15 +7946,15 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.2">
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="31"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.2">
       <c r="L8" s="18" t="s">
